--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2124,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -2368,86 +2368,86 @@
     </row>
     <row r="16" ht="20.4" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
+      <c r="B16" s="48" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="40" t="n"/>
+      <c r="F16" s="40" t="n"/>
       <c r="G16" s="89" t="n"/>
-      <c r="H16" s="91" t="n"/>
-      <c r="I16" s="54" t="n"/>
+      <c r="H16" s="90" t="n"/>
+      <c r="I16" s="53" t="n"/>
       <c r="J16" s="28" t="n"/>
     </row>
     <row r="17" ht="40.8" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="39" t="n"/>
-      <c r="E17" s="40" t="n"/>
-      <c r="F17" s="40" t="n"/>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
       <c r="G17" s="89" t="n"/>
-      <c r="H17" s="90" t="n"/>
-      <c r="I17" s="53" t="n"/>
+      <c r="H17" s="91" t="n"/>
+      <c r="I17" s="54" t="n"/>
       <c r="J17" s="36" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
+      <c r="B18" s="48" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="89" t="n"/>
-      <c r="H18" s="91" t="n"/>
-      <c r="I18" s="54" t="n"/>
+      <c r="H18" s="90" t="n"/>
+      <c r="I18" s="53" t="n"/>
       <c r="J18" s="28" t="n"/>
     </row>
     <row r="19" ht="30.6" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="48" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="39" t="n"/>
-      <c r="E19" s="40" t="n"/>
-      <c r="F19" s="40" t="n"/>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
       <c r="G19" s="89" t="n"/>
-      <c r="H19" s="90" t="n"/>
-      <c r="I19" s="53" t="n"/>
+      <c r="H19" s="91" t="n"/>
+      <c r="I19" s="54" t="n"/>
       <c r="J19" s="36" t="n"/>
     </row>
     <row r="20" ht="30.6" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
+      <c r="B20" s="48" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="40" t="n"/>
       <c r="G20" s="89" t="n"/>
-      <c r="H20" s="91" t="n"/>
-      <c r="I20" s="54" t="n"/>
+      <c r="H20" s="90" t="n"/>
+      <c r="I20" s="53" t="n"/>
       <c r="J20" s="28" t="n"/>
     </row>
     <row r="21" ht="30.6" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="48" t="n"/>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="39" t="n"/>
-      <c r="E21" s="40" t="n"/>
-      <c r="F21" s="40" t="n"/>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
       <c r="G21" s="89" t="n"/>
-      <c r="H21" s="90" t="n"/>
-      <c r="I21" s="53" t="n"/>
+      <c r="H21" s="91" t="n"/>
+      <c r="I21" s="54" t="n"/>
       <c r="J21" s="36" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
+      <c r="B22" s="48" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="40" t="n"/>
+      <c r="F22" s="40" t="n"/>
       <c r="G22" s="89" t="n"/>
-      <c r="H22" s="91" t="n"/>
-      <c r="I22" s="54" t="n"/>
+      <c r="H22" s="90" t="n"/>
+      <c r="I22" s="53" t="n"/>
       <c r="J22" s="28" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -2500,38 +2500,38 @@
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="48" t="n"/>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="39" t="n"/>
-      <c r="E27" s="40" t="n"/>
-      <c r="F27" s="40" t="n"/>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
       <c r="G27" s="89" t="n"/>
-      <c r="H27" s="90" t="n"/>
-      <c r="I27" s="53" t="n"/>
+      <c r="H27" s="91" t="n"/>
+      <c r="I27" s="54" t="n"/>
       <c r="J27" s="36" t="n"/>
     </row>
     <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="49" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="32" t="n"/>
+      <c r="B28" s="48" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="40" t="n"/>
+      <c r="F28" s="40" t="n"/>
       <c r="G28" s="89" t="n"/>
-      <c r="H28" s="91" t="n"/>
-      <c r="I28" s="54" t="n"/>
+      <c r="H28" s="90" t="n"/>
+      <c r="I28" s="53" t="n"/>
       <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="48" t="n"/>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="39" t="n"/>
-      <c r="E29" s="40" t="n"/>
-      <c r="F29" s="40" t="n"/>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="32" t="n"/>
+      <c r="F29" s="32" t="n"/>
       <c r="G29" s="89" t="n"/>
-      <c r="H29" s="90" t="n"/>
-      <c r="I29" s="53" t="n"/>
+      <c r="H29" s="91" t="n"/>
+      <c r="I29" s="54" t="n"/>
       <c r="J29" s="36" t="n"/>
     </row>
     <row r="30" ht="30.6" customHeight="1">
@@ -2668,118 +2668,228 @@
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="69" t="n"/>
-      <c r="C41" s="70" t="n"/>
-      <c r="D41" s="71" t="n"/>
-      <c r="E41" s="72" t="n"/>
-      <c r="F41" s="72" t="n"/>
-      <c r="G41" s="92" t="n"/>
-      <c r="H41" s="93" t="n"/>
-      <c r="I41" s="74" t="n"/>
+      <c r="B41" s="49" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="89" t="n"/>
+      <c r="H41" s="91" t="n"/>
+      <c r="I41" s="54" t="n"/>
       <c r="J41" s="68" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="26.4" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="43" t="n"/>
-      <c r="E42" s="43" t="n"/>
-      <c r="F42" s="43" t="n"/>
-      <c r="G42" s="43" t="n"/>
-      <c r="H42" s="43" t="n"/>
-      <c r="I42" s="43" t="n"/>
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="90" t="n"/>
+      <c r="I42" s="53" t="n"/>
       <c r="J42" s="43" t="n"/>
     </row>
-    <row r="43" ht="15.6" customHeight="1" thickBot="1">
+    <row r="43" ht="26.4" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="91" t="n"/>
+      <c r="I43" s="54" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="12" customHeight="1">
+    <row r="44" ht="26.4" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="58" t="n"/>
-      <c r="C44" s="59" t="n"/>
-      <c r="D44" s="59" t="n"/>
-      <c r="E44" s="59" t="n"/>
-      <c r="F44" s="59" t="n"/>
-      <c r="G44" s="59" t="n"/>
-      <c r="H44" s="59" t="n"/>
-      <c r="I44" s="60" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="53" t="n"/>
       <c r="J44" s="43" t="n"/>
     </row>
-    <row r="45" ht="15.6" customHeight="1">
+    <row r="45" ht="26.4" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="67" t="n"/>
-      <c r="C45" s="64" t="n"/>
-      <c r="D45" s="66" t="n"/>
-      <c r="E45" s="64" t="n"/>
-      <c r="F45" s="64" t="n"/>
-      <c r="G45" s="64" t="n"/>
-      <c r="H45" s="64" t="n"/>
-      <c r="I45" s="65" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="89" t="n"/>
+      <c r="H45" s="91" t="n"/>
+      <c r="I45" s="54" t="n"/>
       <c r="J45" s="43" t="n"/>
     </row>
-    <row r="46" ht="9.6" customHeight="1" thickBot="1">
+    <row r="46" ht="26.4" customHeight="1" thickBot="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="61" t="n"/>
-      <c r="C46" s="62" t="n"/>
-      <c r="D46" s="62" t="n"/>
-      <c r="E46" s="62" t="n"/>
-      <c r="F46" s="62" t="n"/>
-      <c r="G46" s="62" t="n"/>
-      <c r="H46" s="62" t="n"/>
-      <c r="I46" s="63" t="n"/>
+      <c r="B46" s="48" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="40" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="53" t="n"/>
       <c r="J46" s="43" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="26.4" customHeight="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="43" t="n"/>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
-      <c r="F47" s="43" t="n"/>
-      <c r="G47" s="43" t="n"/>
-      <c r="H47" s="43" t="n"/>
-      <c r="I47" s="43" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="91" t="n"/>
+      <c r="I47" s="54" t="n"/>
       <c r="J47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="26.4" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="47" t="n"/>
-      <c r="C48" s="47" t="n"/>
-      <c r="D48" s="47" t="n"/>
-      <c r="E48" s="47" t="n"/>
-      <c r="F48" s="47" t="n"/>
-      <c r="G48" s="47" t="n"/>
-      <c r="H48" s="47" t="n"/>
-      <c r="I48" s="47" t="n"/>
+      <c r="B48" s="48" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="90" t="n"/>
+      <c r="I48" s="53" t="n"/>
       <c r="J48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="26.4" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="43" t="n"/>
-      <c r="C49" s="43" t="n"/>
-      <c r="D49" s="43" t="n"/>
-      <c r="E49" s="43" t="n"/>
-      <c r="F49" s="43" t="n"/>
-      <c r="G49" s="43" t="n"/>
-      <c r="H49" s="43" t="n"/>
-      <c r="I49" s="43" t="n"/>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="89" t="n"/>
+      <c r="H49" s="91" t="n"/>
+      <c r="I49" s="54" t="n"/>
       <c r="J49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="26.4" customHeight="1">
+      <c r="B50" s="48" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="89" t="n"/>
+      <c r="H50" s="90" t="n"/>
+      <c r="I50" s="53" t="n"/>
+    </row>
+    <row r="51" ht="26.4" customHeight="1">
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="89" t="n"/>
+      <c r="H51" s="91" t="n"/>
+      <c r="I51" s="54" t="n"/>
+    </row>
+    <row r="52" ht="26.4" customHeight="1">
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="40" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="90" t="n"/>
+      <c r="I52" s="53" t="n"/>
+    </row>
+    <row r="53" ht="26.4" customHeight="1">
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="91" t="n"/>
+      <c r="I53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="26.4" customHeight="1">
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="89" t="n"/>
+      <c r="H54" s="90" t="n"/>
+      <c r="I54" s="53" t="n"/>
+    </row>
+    <row r="55" ht="26.4" customHeight="1">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="30" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="89" t="n"/>
+      <c r="H55" s="91" t="n"/>
+      <c r="I55" s="54" t="n"/>
+    </row>
+    <row r="56" ht="26.4" customHeight="1">
+      <c r="B56" s="48" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="89" t="n"/>
+      <c r="H56" s="90" t="n"/>
+      <c r="I56" s="53" t="n"/>
+    </row>
+    <row r="57" ht="26.4" customHeight="1">
+      <c r="B57" s="49" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="91" t="n"/>
+      <c r="I57" s="54" t="n"/>
+    </row>
+    <row r="58" ht="26.4" customHeight="1">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="40" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="90" t="n"/>
+      <c r="I58" s="53" t="n"/>
+    </row>
+    <row r="59" ht="26.4" customHeight="1">
+      <c r="B59" s="49" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="91" t="n"/>
+      <c r="I59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="26.4" customHeight="1">
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="90" t="n"/>
+      <c r="I60" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G41">
+  <conditionalFormatting sqref="G8:G60">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3644,7 +3754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I535"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -3694,540 +3804,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4254,7 +3830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4808,108 +4384,218 @@
       <c r="I41" s="54" t="n"/>
       <c r="J41" s="28" t="n"/>
     </row>
-    <row r="42" ht="24.6" customHeight="1" thickBot="1">
+    <row r="42" ht="24" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="78" t="n"/>
-      <c r="E42" s="79" t="n"/>
-      <c r="F42" s="79" t="n"/>
-      <c r="G42" s="92" t="n"/>
-      <c r="H42" s="96" t="n"/>
-      <c r="I42" s="81" t="n"/>
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="90" t="n"/>
+      <c r="I42" s="53" t="n"/>
       <c r="J42" s="75" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="91" t="n"/>
+      <c r="I43" s="54" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1" thickBot="1">
+    <row r="44" ht="24" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="53" t="n"/>
       <c r="J44" s="43" t="n"/>
     </row>
-    <row r="45" ht="10.2" customHeight="1">
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="58" t="n"/>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-      <c r="G45" s="59" t="n"/>
-      <c r="H45" s="59" t="n"/>
-      <c r="I45" s="60" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="89" t="n"/>
+      <c r="H45" s="91" t="n"/>
+      <c r="I45" s="54" t="n"/>
       <c r="J45" s="43" t="n"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="64" t="n"/>
-      <c r="D46" s="64" t="n"/>
-      <c r="E46" s="64" t="n"/>
-      <c r="F46" s="64" t="n"/>
-      <c r="G46" s="64" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="65" t="n"/>
+      <c r="B46" s="48" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="40" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="53" t="n"/>
       <c r="J46" s="43" t="n"/>
     </row>
-    <row r="47" ht="10.8" customHeight="1" thickBot="1">
+    <row r="47" ht="24" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="62" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="62" t="n"/>
-      <c r="I47" s="63" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="91" t="n"/>
+      <c r="I47" s="54" t="n"/>
       <c r="J47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="43" t="n"/>
-      <c r="F48" s="43" t="n"/>
-      <c r="G48" s="43" t="n"/>
-      <c r="H48" s="43" t="n"/>
-      <c r="I48" s="43" t="n"/>
+      <c r="B48" s="48" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="90" t="n"/>
+      <c r="I48" s="53" t="n"/>
       <c r="J48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="47" t="n"/>
-      <c r="C49" s="47" t="n"/>
-      <c r="D49" s="47" t="n"/>
-      <c r="E49" s="47" t="n"/>
-      <c r="F49" s="47" t="n"/>
-      <c r="G49" s="47" t="n"/>
-      <c r="H49" s="47" t="n"/>
-      <c r="I49" s="47" t="n"/>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="89" t="n"/>
+      <c r="H49" s="91" t="n"/>
+      <c r="I49" s="54" t="n"/>
       <c r="J49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="B50" s="48" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="89" t="n"/>
+      <c r="H50" s="90" t="n"/>
+      <c r="I50" s="53" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="89" t="n"/>
+      <c r="H51" s="91" t="n"/>
+      <c r="I51" s="54" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="40" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="90" t="n"/>
+      <c r="I52" s="53" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="91" t="n"/>
+      <c r="I53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="89" t="n"/>
+      <c r="H54" s="90" t="n"/>
+      <c r="I54" s="53" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="30" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="89" t="n"/>
+      <c r="H55" s="91" t="n"/>
+      <c r="I55" s="54" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="48" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="89" t="n"/>
+      <c r="H56" s="90" t="n"/>
+      <c r="I56" s="53" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="B57" s="49" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="91" t="n"/>
+      <c r="I57" s="54" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="40" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="90" t="n"/>
+      <c r="I58" s="53" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="B59" s="49" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="91" t="n"/>
+      <c r="I59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="90" t="n"/>
+      <c r="I60" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G42">
+  <conditionalFormatting sqref="G8:G60">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
@@ -5774,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I500"/>
+  <dimension ref="A1:I415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5824,509 +5510,12 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
     <row r="112" ht="409.6" customHeight="1">
       <c r="I112" s="56" t="n"/>
     </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
     <row r="415" ht="409.6" customHeight="1">
       <c r="I415" s="56" t="n"/>
     </row>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30720" yWindow="0" windowWidth="21600" windowHeight="11235" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -686,21 +686,42 @@
     <xf numFmtId="164" fontId="20" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2124,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -2134,10 +2155,10 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="14" customWidth="1" style="14" min="8" max="8"/>
-    <col width="56" customWidth="1" style="11" min="9" max="9"/>
-    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="11" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="11" min="9" max="9"/>
+    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
     <col width="8.88671875" customWidth="1" style="11" min="14" max="14"/>
@@ -2163,10 +2184,7 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84">
-        <f>Date!B2</f>
-        <v/>
-      </c>
+      <c r="H2" s="84" t="n"/>
       <c r="J2" s="83" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -2260,15 +2278,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -2279,8 +2302,9 @@
       <c r="F8" s="40" t="n"/>
       <c r="G8" s="89" t="n"/>
       <c r="H8" s="90" t="n"/>
-      <c r="I8" s="53" t="n"/>
-      <c r="J8" s="36" t="n"/>
+      <c r="I8" s="91" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="26.4" customHeight="1">
       <c r="A9" s="28" t="n"/>
@@ -2290,9 +2314,10 @@
       <c r="E9" s="32" t="n"/>
       <c r="F9" s="32" t="n"/>
       <c r="G9" s="89" t="n"/>
-      <c r="H9" s="91" t="n"/>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="28" t="n"/>
+      <c r="H9" s="92" t="n"/>
+      <c r="I9" s="93" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="20.4" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -2303,8 +2328,9 @@
       <c r="F10" s="40" t="n"/>
       <c r="G10" s="89" t="n"/>
       <c r="H10" s="90" t="n"/>
-      <c r="I10" s="53" t="n"/>
-      <c r="J10" s="36" t="n"/>
+      <c r="I10" s="91" t="n"/>
+      <c r="J10" s="53" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="20.4" customHeight="1">
       <c r="A11" s="28" t="n"/>
@@ -2314,9 +2340,10 @@
       <c r="E11" s="32" t="n"/>
       <c r="F11" s="32" t="n"/>
       <c r="G11" s="89" t="n"/>
-      <c r="H11" s="91" t="n"/>
-      <c r="I11" s="54" t="n"/>
-      <c r="J11" s="28" t="n"/>
+      <c r="H11" s="92" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="20.4" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -2327,8 +2354,9 @@
       <c r="F12" s="40" t="n"/>
       <c r="G12" s="89" t="n"/>
       <c r="H12" s="90" t="n"/>
-      <c r="I12" s="53" t="n"/>
-      <c r="J12" s="36" t="n"/>
+      <c r="I12" s="91" t="n"/>
+      <c r="J12" s="53" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="28" t="n"/>
@@ -2338,9 +2366,10 @@
       <c r="E13" s="32" t="n"/>
       <c r="F13" s="32" t="n"/>
       <c r="G13" s="89" t="n"/>
-      <c r="H13" s="91" t="n"/>
-      <c r="I13" s="54" t="n"/>
-      <c r="J13" s="28" t="n"/>
+      <c r="H13" s="92" t="n"/>
+      <c r="I13" s="93" t="n"/>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="36" t="n"/>
@@ -2351,8 +2380,9 @@
       <c r="F14" s="40" t="n"/>
       <c r="G14" s="89" t="n"/>
       <c r="H14" s="90" t="n"/>
-      <c r="I14" s="53" t="n"/>
-      <c r="J14" s="36" t="n"/>
+      <c r="I14" s="91" t="n"/>
+      <c r="J14" s="53" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="28" t="n"/>
@@ -2362,93 +2392,101 @@
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="32" t="n"/>
       <c r="G15" s="89" t="n"/>
-      <c r="H15" s="91" t="n"/>
-      <c r="I15" s="54" t="n"/>
-      <c r="J15" s="28" t="n"/>
+      <c r="H15" s="92" t="n"/>
+      <c r="I15" s="93" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="20.4" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="48" t="n"/>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="39" t="n"/>
-      <c r="E16" s="40" t="n"/>
-      <c r="F16" s="40" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
       <c r="G16" s="89" t="n"/>
-      <c r="H16" s="90" t="n"/>
-      <c r="I16" s="53" t="n"/>
-      <c r="J16" s="28" t="n"/>
+      <c r="H16" s="92" t="n"/>
+      <c r="I16" s="93" t="n"/>
+      <c r="J16" s="54" t="n"/>
+      <c r="K16" s="28" t="n"/>
     </row>
     <row r="17" ht="40.8" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
+      <c r="B17" s="48" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="89" t="n"/>
-      <c r="H17" s="91" t="n"/>
-      <c r="I17" s="54" t="n"/>
-      <c r="J17" s="36" t="n"/>
+      <c r="H17" s="90" t="n"/>
+      <c r="I17" s="91" t="n"/>
+      <c r="J17" s="53" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="48" t="n"/>
-      <c r="C18" s="38" t="n"/>
-      <c r="D18" s="39" t="n"/>
-      <c r="E18" s="40" t="n"/>
-      <c r="F18" s="40" t="n"/>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
       <c r="G18" s="89" t="n"/>
-      <c r="H18" s="90" t="n"/>
-      <c r="I18" s="53" t="n"/>
-      <c r="J18" s="28" t="n"/>
+      <c r="H18" s="92" t="n"/>
+      <c r="I18" s="93" t="n"/>
+      <c r="J18" s="54" t="n"/>
+      <c r="K18" s="28" t="n"/>
     </row>
     <row r="19" ht="30.6" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
+      <c r="B19" s="48" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="40" t="n"/>
       <c r="G19" s="89" t="n"/>
-      <c r="H19" s="91" t="n"/>
-      <c r="I19" s="54" t="n"/>
-      <c r="J19" s="36" t="n"/>
+      <c r="H19" s="90" t="n"/>
+      <c r="I19" s="91" t="n"/>
+      <c r="J19" s="53" t="n"/>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="30.6" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="48" t="n"/>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="39" t="n"/>
-      <c r="E20" s="40" t="n"/>
-      <c r="F20" s="40" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
       <c r="G20" s="89" t="n"/>
-      <c r="H20" s="90" t="n"/>
-      <c r="I20" s="53" t="n"/>
-      <c r="J20" s="28" t="n"/>
+      <c r="H20" s="92" t="n"/>
+      <c r="I20" s="93" t="n"/>
+      <c r="J20" s="54" t="n"/>
+      <c r="K20" s="28" t="n"/>
     </row>
     <row r="21" ht="30.6" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="40" t="n"/>
       <c r="G21" s="89" t="n"/>
-      <c r="H21" s="91" t="n"/>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="36" t="n"/>
+      <c r="H21" s="90" t="n"/>
+      <c r="I21" s="91" t="n"/>
+      <c r="J21" s="53" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="48" t="n"/>
-      <c r="C22" s="38" t="n"/>
-      <c r="D22" s="39" t="n"/>
-      <c r="E22" s="40" t="n"/>
-      <c r="F22" s="40" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="32" t="n"/>
+      <c r="F22" s="32" t="n"/>
       <c r="G22" s="89" t="n"/>
-      <c r="H22" s="90" t="n"/>
-      <c r="I22" s="53" t="n"/>
-      <c r="J22" s="28" t="n"/>
+      <c r="H22" s="92" t="n"/>
+      <c r="I22" s="93" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="28" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="28" t="n"/>
@@ -2458,9 +2496,10 @@
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="89" t="n"/>
-      <c r="H23" s="91" t="n"/>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="28" t="n"/>
+      <c r="H23" s="92" t="n"/>
+      <c r="I23" s="93" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -2471,8 +2510,9 @@
       <c r="F24" s="40" t="n"/>
       <c r="G24" s="89" t="n"/>
       <c r="H24" s="90" t="n"/>
-      <c r="I24" s="53" t="n"/>
-      <c r="J24" s="36" t="n"/>
+      <c r="I24" s="91" t="n"/>
+      <c r="J24" s="53" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="28" t="n"/>
@@ -2482,9 +2522,10 @@
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="89" t="n"/>
-      <c r="H25" s="91" t="n"/>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="28" t="n"/>
+      <c r="H25" s="92" t="n"/>
+      <c r="I25" s="93" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="20.4" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -2495,44 +2536,48 @@
       <c r="F26" s="40" t="n"/>
       <c r="G26" s="89" t="n"/>
       <c r="H26" s="90" t="n"/>
-      <c r="I26" s="53" t="n"/>
-      <c r="J26" s="36" t="n"/>
+      <c r="I26" s="91" t="n"/>
+      <c r="J26" s="53" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="49" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
+      <c r="B27" s="48" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="40" t="n"/>
+      <c r="F27" s="40" t="n"/>
       <c r="G27" s="89" t="n"/>
-      <c r="H27" s="91" t="n"/>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="36" t="n"/>
+      <c r="H27" s="90" t="n"/>
+      <c r="I27" s="91" t="n"/>
+      <c r="J27" s="53" t="n"/>
+      <c r="K27" s="36" t="n"/>
     </row>
     <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="48" t="n"/>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="39" t="n"/>
-      <c r="E28" s="40" t="n"/>
-      <c r="F28" s="40" t="n"/>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
       <c r="G28" s="89" t="n"/>
-      <c r="H28" s="90" t="n"/>
-      <c r="I28" s="53" t="n"/>
-      <c r="J28" s="28" t="n"/>
+      <c r="H28" s="92" t="n"/>
+      <c r="I28" s="93" t="n"/>
+      <c r="J28" s="54" t="n"/>
+      <c r="K28" s="28" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="49" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="32" t="n"/>
-      <c r="F29" s="32" t="n"/>
+      <c r="B29" s="48" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="40" t="n"/>
+      <c r="F29" s="40" t="n"/>
       <c r="G29" s="89" t="n"/>
-      <c r="H29" s="91" t="n"/>
-      <c r="I29" s="54" t="n"/>
-      <c r="J29" s="36" t="n"/>
+      <c r="H29" s="90" t="n"/>
+      <c r="I29" s="91" t="n"/>
+      <c r="J29" s="53" t="n"/>
+      <c r="K29" s="36" t="n"/>
     </row>
     <row r="30" ht="30.6" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -2543,8 +2588,9 @@
       <c r="F30" s="40" t="n"/>
       <c r="G30" s="89" t="n"/>
       <c r="H30" s="90" t="n"/>
-      <c r="I30" s="53" t="n"/>
-      <c r="J30" s="36" t="n"/>
+      <c r="I30" s="91" t="n"/>
+      <c r="J30" s="53" t="n"/>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="30.6" customHeight="1">
       <c r="A31" s="28" t="n"/>
@@ -2554,9 +2600,10 @@
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="89" t="n"/>
-      <c r="H31" s="91" t="n"/>
-      <c r="I31" s="54" t="n"/>
-      <c r="J31" s="28" t="n"/>
+      <c r="H31" s="92" t="n"/>
+      <c r="I31" s="93" t="n"/>
+      <c r="J31" s="54" t="n"/>
+      <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -2567,8 +2614,9 @@
       <c r="F32" s="40" t="n"/>
       <c r="G32" s="89" t="n"/>
       <c r="H32" s="90" t="n"/>
-      <c r="I32" s="53" t="n"/>
-      <c r="J32" s="36" t="n"/>
+      <c r="I32" s="91" t="n"/>
+      <c r="J32" s="53" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
@@ -2578,9 +2626,10 @@
       <c r="E33" s="32" t="n"/>
       <c r="F33" s="32" t="n"/>
       <c r="G33" s="89" t="n"/>
-      <c r="H33" s="91" t="n"/>
-      <c r="I33" s="54" t="n"/>
-      <c r="J33" s="28" t="n"/>
+      <c r="H33" s="92" t="n"/>
+      <c r="I33" s="93" t="n"/>
+      <c r="J33" s="54" t="n"/>
+      <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="30.6" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -2591,8 +2640,9 @@
       <c r="F34" s="40" t="n"/>
       <c r="G34" s="89" t="n"/>
       <c r="H34" s="90" t="n"/>
-      <c r="I34" s="53" t="n"/>
-      <c r="J34" s="36" t="n"/>
+      <c r="I34" s="91" t="n"/>
+      <c r="J34" s="53" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="30.6" customHeight="1">
       <c r="A35" s="28" t="n"/>
@@ -2602,9 +2652,10 @@
       <c r="E35" s="32" t="n"/>
       <c r="F35" s="32" t="n"/>
       <c r="G35" s="89" t="n"/>
-      <c r="H35" s="91" t="n"/>
-      <c r="I35" s="54" t="n"/>
-      <c r="J35" s="28" t="n"/>
+      <c r="H35" s="92" t="n"/>
+      <c r="I35" s="93" t="n"/>
+      <c r="J35" s="54" t="n"/>
+      <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -2615,8 +2666,9 @@
       <c r="F36" s="40" t="n"/>
       <c r="G36" s="89" t="n"/>
       <c r="H36" s="90" t="n"/>
-      <c r="I36" s="53" t="n"/>
-      <c r="J36" s="36" t="n"/>
+      <c r="I36" s="91" t="n"/>
+      <c r="J36" s="53" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
@@ -2626,9 +2678,10 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="89" t="n"/>
-      <c r="H37" s="91" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="28" t="n"/>
+      <c r="H37" s="92" t="n"/>
+      <c r="I37" s="93" t="n"/>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -2639,8 +2692,9 @@
       <c r="F38" s="40" t="n"/>
       <c r="G38" s="89" t="n"/>
       <c r="H38" s="90" t="n"/>
-      <c r="I38" s="53" t="n"/>
-      <c r="J38" s="36" t="n"/>
+      <c r="I38" s="91" t="n"/>
+      <c r="J38" s="53" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
@@ -2650,9 +2704,10 @@
       <c r="E39" s="32" t="n"/>
       <c r="F39" s="32" t="n"/>
       <c r="G39" s="89" t="n"/>
-      <c r="H39" s="91" t="n"/>
-      <c r="I39" s="54" t="n"/>
-      <c r="J39" s="28" t="n"/>
+      <c r="H39" s="92" t="n"/>
+      <c r="I39" s="93" t="n"/>
+      <c r="J39" s="54" t="n"/>
+      <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="20.4" customHeight="1">
       <c r="A40" s="36" t="n"/>
@@ -2663,233 +2718,133 @@
       <c r="F40" s="40" t="n"/>
       <c r="G40" s="89" t="n"/>
       <c r="H40" s="90" t="n"/>
-      <c r="I40" s="53" t="n"/>
-      <c r="J40" s="36" t="n"/>
+      <c r="I40" s="91" t="n"/>
+      <c r="J40" s="53" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="68" t="n"/>
-    </row>
-    <row r="42" ht="26.4" customHeight="1">
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="72" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="94" t="n"/>
+      <c r="H41" s="95" t="n"/>
+      <c r="I41" s="96" t="n"/>
+      <c r="J41" s="74" t="n"/>
+      <c r="K41" s="68" t="n"/>
+    </row>
+    <row r="42">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="48" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="90" t="n"/>
-      <c r="I42" s="53" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="43" t="n"/>
+      <c r="E42" s="43" t="n"/>
+      <c r="F42" s="43" t="n"/>
+      <c r="G42" s="43" t="n"/>
+      <c r="H42" s="97" t="n"/>
+      <c r="I42" s="43" t="n"/>
       <c r="J42" s="43" t="n"/>
-    </row>
-    <row r="43" ht="26.4" customHeight="1" thickBot="1">
+      <c r="K42" s="43" t="n"/>
+    </row>
+    <row r="43" ht="15.6" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="91" t="n"/>
-      <c r="I43" s="54" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="97" t="n"/>
+      <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="26.4" customHeight="1">
+      <c r="K43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="12" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="48" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="90" t="n"/>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="43" t="n"/>
-    </row>
-    <row r="45" ht="26.4" customHeight="1">
+      <c r="B44" s="58" t="n"/>
+      <c r="C44" s="59" t="n"/>
+      <c r="D44" s="59" t="n"/>
+      <c r="E44" s="59" t="n"/>
+      <c r="F44" s="59" t="n"/>
+      <c r="G44" s="59" t="n"/>
+      <c r="H44" s="98" t="n"/>
+      <c r="I44" s="59" t="n"/>
+      <c r="J44" s="60" t="n"/>
+      <c r="K44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="15.6" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="91" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="43" t="n"/>
-    </row>
-    <row r="46" ht="26.4" customHeight="1" thickBot="1">
+      <c r="B45" s="67" t="n"/>
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="66" t="n"/>
+      <c r="E45" s="64" t="n"/>
+      <c r="F45" s="64" t="n"/>
+      <c r="G45" s="64" t="n"/>
+      <c r="H45" s="99" t="n"/>
+      <c r="I45" s="64" t="n"/>
+      <c r="J45" s="65" t="n"/>
+      <c r="K45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="9.6" customHeight="1" thickBot="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="26.4" customHeight="1">
+      <c r="B46" s="61" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="100" t="n"/>
+      <c r="I46" s="62" t="n"/>
+      <c r="J46" s="63" t="n"/>
+      <c r="K46" s="43" t="n"/>
+    </row>
+    <row r="47">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="49" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="91" t="n"/>
-      <c r="I47" s="54" t="n"/>
+      <c r="B47" s="43" t="n"/>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="43" t="n"/>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="43" t="n"/>
+      <c r="H47" s="97" t="n"/>
+      <c r="I47" s="43" t="n"/>
       <c r="J47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="26.4" customHeight="1">
+      <c r="K47" s="43" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="40" t="n"/>
-      <c r="F48" s="40" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="90" t="n"/>
-      <c r="I48" s="53" t="n"/>
-      <c r="J48" s="43" t="n"/>
-    </row>
-    <row r="49" ht="26.4" customHeight="1">
+      <c r="B48" s="47" t="n"/>
+      <c r="C48" s="47" t="n"/>
+      <c r="D48" s="47" t="n"/>
+      <c r="E48" s="47" t="n"/>
+      <c r="F48" s="47" t="n"/>
+      <c r="G48" s="47" t="n"/>
+      <c r="H48" s="101" t="n"/>
+      <c r="I48" s="47" t="n"/>
+      <c r="J48" s="47" t="n"/>
+      <c r="K48" s="43" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="49" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="91" t="n"/>
-      <c r="I49" s="54" t="n"/>
+      <c r="B49" s="43" t="n"/>
+      <c r="C49" s="43" t="n"/>
+      <c r="D49" s="43" t="n"/>
+      <c r="E49" s="43" t="n"/>
+      <c r="F49" s="43" t="n"/>
+      <c r="G49" s="43" t="n"/>
+      <c r="H49" s="97" t="n"/>
+      <c r="I49" s="43" t="n"/>
       <c r="J49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="26.4" customHeight="1">
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="90" t="n"/>
-      <c r="I50" s="53" t="n"/>
-    </row>
-    <row r="51" ht="26.4" customHeight="1">
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="91" t="n"/>
-      <c r="I51" s="54" t="n"/>
-    </row>
-    <row r="52" ht="26.4" customHeight="1">
-      <c r="B52" s="48" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="40" t="n"/>
-      <c r="F52" s="40" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="90" t="n"/>
-      <c r="I52" s="53" t="n"/>
-    </row>
-    <row r="53" ht="26.4" customHeight="1">
-      <c r="B53" s="49" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="89" t="n"/>
-      <c r="H53" s="91" t="n"/>
-      <c r="I53" s="54" t="n"/>
-    </row>
-    <row r="54" ht="26.4" customHeight="1">
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="89" t="n"/>
-      <c r="H54" s="90" t="n"/>
-      <c r="I54" s="53" t="n"/>
-    </row>
-    <row r="55" ht="26.4" customHeight="1">
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="89" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="54" t="n"/>
-    </row>
-    <row r="56" ht="26.4" customHeight="1">
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
-      <c r="G56" s="89" t="n"/>
-      <c r="H56" s="90" t="n"/>
-      <c r="I56" s="53" t="n"/>
-    </row>
-    <row r="57" ht="26.4" customHeight="1">
-      <c r="B57" s="49" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="89" t="n"/>
-      <c r="H57" s="91" t="n"/>
-      <c r="I57" s="54" t="n"/>
-    </row>
-    <row r="58" ht="26.4" customHeight="1">
-      <c r="B58" s="48" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
-      <c r="G58" s="89" t="n"/>
-      <c r="H58" s="90" t="n"/>
-      <c r="I58" s="53" t="n"/>
-    </row>
-    <row r="59" ht="26.4" customHeight="1">
-      <c r="B59" s="49" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
-      <c r="G59" s="89" t="n"/>
-      <c r="H59" s="91" t="n"/>
-      <c r="I59" s="54" t="n"/>
-    </row>
-    <row r="60" ht="26.4" customHeight="1">
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="40" t="n"/>
-      <c r="F60" s="40" t="n"/>
-      <c r="G60" s="89" t="n"/>
-      <c r="H60" s="90" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G60">
+  <conditionalFormatting sqref="G8:G41">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3017,14 +2972,14 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="94" t="n"/>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
-      <c r="G11" s="94" t="n"/>
-      <c r="H11" s="94" t="n"/>
-      <c r="I11" s="94" t="n"/>
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="102" t="n"/>
+      <c r="D11" s="102" t="n"/>
+      <c r="E11" s="102" t="n"/>
+      <c r="F11" s="102" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
@@ -3100,7 +3055,7 @@
     <row r="13" ht="15.6" customHeight="1" thickBot="1">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="95" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="38" t="n"/>
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="40" t="n"/>
@@ -3754,7 +3709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -3804,6 +3759,540 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3830,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -3840,10 +4329,10 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="14" customWidth="1" style="14" min="8" max="8"/>
-    <col width="56" customWidth="1" style="11" min="9" max="9"/>
-    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="11" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="11" min="9" max="9"/>
+    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
     <col width="8.88671875" customWidth="1" style="11" min="14" max="14"/>
@@ -3869,10 +4358,7 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84">
-        <f>Date!B2</f>
-        <v/>
-      </c>
+      <c r="H2" s="84" t="n"/>
       <c r="J2" s="83" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -3966,15 +4452,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -3985,8 +4476,9 @@
       <c r="F8" s="40" t="n"/>
       <c r="G8" s="89" t="n"/>
       <c r="H8" s="90" t="n"/>
-      <c r="I8" s="53" t="n"/>
-      <c r="J8" s="36" t="n"/>
+      <c r="I8" s="91" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="28" t="n"/>
@@ -3996,9 +4488,10 @@
       <c r="E9" s="32" t="n"/>
       <c r="F9" s="32" t="n"/>
       <c r="G9" s="89" t="n"/>
-      <c r="H9" s="91" t="n"/>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="28" t="n"/>
+      <c r="H9" s="92" t="n"/>
+      <c r="I9" s="93" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="20.4" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -4009,8 +4502,9 @@
       <c r="F10" s="40" t="n"/>
       <c r="G10" s="89" t="n"/>
       <c r="H10" s="90" t="n"/>
-      <c r="I10" s="53" t="n"/>
-      <c r="J10" s="36" t="n"/>
+      <c r="I10" s="91" t="n"/>
+      <c r="J10" s="53" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="28" t="n"/>
@@ -4020,9 +4514,10 @@
       <c r="E11" s="32" t="n"/>
       <c r="F11" s="32" t="n"/>
       <c r="G11" s="89" t="n"/>
-      <c r="H11" s="91" t="n"/>
-      <c r="I11" s="54" t="n"/>
-      <c r="J11" s="28" t="n"/>
+      <c r="H11" s="92" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -4033,8 +4528,9 @@
       <c r="F12" s="40" t="n"/>
       <c r="G12" s="89" t="n"/>
       <c r="H12" s="90" t="n"/>
-      <c r="I12" s="53" t="n"/>
-      <c r="J12" s="36" t="n"/>
+      <c r="I12" s="91" t="n"/>
+      <c r="J12" s="53" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="20.4" customHeight="1">
       <c r="A13" s="28" t="n"/>
@@ -4044,9 +4540,10 @@
       <c r="E13" s="32" t="n"/>
       <c r="F13" s="32" t="n"/>
       <c r="G13" s="89" t="n"/>
-      <c r="H13" s="91" t="n"/>
-      <c r="I13" s="54" t="n"/>
-      <c r="J13" s="28" t="n"/>
+      <c r="H13" s="92" t="n"/>
+      <c r="I13" s="93" t="n"/>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14" ht="40.8" customHeight="1">
       <c r="A14" s="36" t="n"/>
@@ -4057,8 +4554,9 @@
       <c r="F14" s="40" t="n"/>
       <c r="G14" s="89" t="n"/>
       <c r="H14" s="90" t="n"/>
-      <c r="I14" s="53" t="n"/>
-      <c r="J14" s="36" t="n"/>
+      <c r="I14" s="91" t="n"/>
+      <c r="J14" s="53" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="30.6" customHeight="1">
       <c r="A15" s="28" t="n"/>
@@ -4068,9 +4566,10 @@
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="32" t="n"/>
       <c r="G15" s="89" t="n"/>
-      <c r="H15" s="91" t="n"/>
-      <c r="I15" s="54" t="n"/>
-      <c r="J15" s="28" t="n"/>
+      <c r="H15" s="92" t="n"/>
+      <c r="I15" s="93" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -4081,8 +4580,9 @@
       <c r="F16" s="40" t="n"/>
       <c r="G16" s="89" t="n"/>
       <c r="H16" s="90" t="n"/>
-      <c r="I16" s="53" t="n"/>
-      <c r="J16" s="36" t="n"/>
+      <c r="I16" s="91" t="n"/>
+      <c r="J16" s="53" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="30.6" customHeight="1">
       <c r="A17" s="28" t="n"/>
@@ -4092,9 +4592,10 @@
       <c r="E17" s="32" t="n"/>
       <c r="F17" s="32" t="n"/>
       <c r="G17" s="89" t="n"/>
-      <c r="H17" s="91" t="n"/>
-      <c r="I17" s="54" t="n"/>
-      <c r="J17" s="28" t="n"/>
+      <c r="H17" s="92" t="n"/>
+      <c r="I17" s="93" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="28" t="n"/>
     </row>
     <row r="18" ht="20.4" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -4105,8 +4606,9 @@
       <c r="F18" s="40" t="n"/>
       <c r="G18" s="89" t="n"/>
       <c r="H18" s="90" t="n"/>
-      <c r="I18" s="53" t="n"/>
-      <c r="J18" s="36" t="n"/>
+      <c r="I18" s="91" t="n"/>
+      <c r="J18" s="53" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="20.4" customHeight="1">
       <c r="A19" s="28" t="n"/>
@@ -4116,9 +4618,10 @@
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="32" t="n"/>
       <c r="G19" s="89" t="n"/>
-      <c r="H19" s="91" t="n"/>
-      <c r="I19" s="54" t="n"/>
-      <c r="J19" s="28" t="n"/>
+      <c r="H19" s="92" t="n"/>
+      <c r="I19" s="93" t="n"/>
+      <c r="J19" s="54" t="n"/>
+      <c r="K19" s="28" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -4129,8 +4632,9 @@
       <c r="F20" s="40" t="n"/>
       <c r="G20" s="89" t="n"/>
       <c r="H20" s="90" t="n"/>
-      <c r="I20" s="53" t="n"/>
-      <c r="J20" s="36" t="n"/>
+      <c r="I20" s="91" t="n"/>
+      <c r="J20" s="53" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21" ht="20.4" customHeight="1">
       <c r="A21" s="28" t="n"/>
@@ -4140,9 +4644,10 @@
       <c r="E21" s="32" t="n"/>
       <c r="F21" s="32" t="n"/>
       <c r="G21" s="89" t="n"/>
-      <c r="H21" s="91" t="n"/>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="28" t="n"/>
+      <c r="H21" s="92" t="n"/>
+      <c r="I21" s="93" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="28" t="n"/>
     </row>
     <row r="22" ht="30.6" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -4153,8 +4658,9 @@
       <c r="F22" s="40" t="n"/>
       <c r="G22" s="89" t="n"/>
       <c r="H22" s="90" t="n"/>
-      <c r="I22" s="53" t="n"/>
-      <c r="J22" s="36" t="n"/>
+      <c r="I22" s="91" t="n"/>
+      <c r="J22" s="53" t="n"/>
+      <c r="K22" s="36" t="n"/>
     </row>
     <row r="23" ht="20.4" customHeight="1">
       <c r="A23" s="28" t="n"/>
@@ -4164,9 +4670,10 @@
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="89" t="n"/>
-      <c r="H23" s="91" t="n"/>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="28" t="n"/>
+      <c r="H23" s="92" t="n"/>
+      <c r="I23" s="93" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -4177,8 +4684,9 @@
       <c r="F24" s="40" t="n"/>
       <c r="G24" s="89" t="n"/>
       <c r="H24" s="90" t="n"/>
-      <c r="I24" s="53" t="n"/>
-      <c r="J24" s="36" t="n"/>
+      <c r="I24" s="91" t="n"/>
+      <c r="J24" s="53" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="30.6" customHeight="1">
       <c r="A25" s="28" t="n"/>
@@ -4188,9 +4696,10 @@
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="89" t="n"/>
-      <c r="H25" s="91" t="n"/>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="28" t="n"/>
+      <c r="H25" s="92" t="n"/>
+      <c r="I25" s="93" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="30.6" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -4201,8 +4710,9 @@
       <c r="F26" s="40" t="n"/>
       <c r="G26" s="89" t="n"/>
       <c r="H26" s="90" t="n"/>
-      <c r="I26" s="53" t="n"/>
-      <c r="J26" s="36" t="n"/>
+      <c r="I26" s="91" t="n"/>
+      <c r="J26" s="53" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="30.6" customHeight="1">
       <c r="A27" s="28" t="n"/>
@@ -4212,9 +4722,10 @@
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="89" t="n"/>
-      <c r="H27" s="91" t="n"/>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="28" t="n"/>
+      <c r="H27" s="92" t="n"/>
+      <c r="I27" s="93" t="n"/>
+      <c r="J27" s="54" t="n"/>
+      <c r="K27" s="28" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -4225,8 +4736,9 @@
       <c r="F28" s="40" t="n"/>
       <c r="G28" s="89" t="n"/>
       <c r="H28" s="90" t="n"/>
-      <c r="I28" s="53" t="n"/>
-      <c r="J28" s="36" t="n"/>
+      <c r="I28" s="91" t="n"/>
+      <c r="J28" s="53" t="n"/>
+      <c r="K28" s="36" t="n"/>
     </row>
     <row r="29" ht="20.4" customHeight="1">
       <c r="A29" s="28" t="n"/>
@@ -4236,9 +4748,10 @@
       <c r="E29" s="32" t="n"/>
       <c r="F29" s="32" t="n"/>
       <c r="G29" s="89" t="n"/>
-      <c r="H29" s="91" t="n"/>
-      <c r="I29" s="54" t="n"/>
-      <c r="J29" s="28" t="n"/>
+      <c r="H29" s="92" t="n"/>
+      <c r="I29" s="93" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="28" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="36" t="n"/>
@@ -4249,8 +4762,9 @@
       <c r="F30" s="40" t="n"/>
       <c r="G30" s="89" t="n"/>
       <c r="H30" s="90" t="n"/>
-      <c r="I30" s="53" t="n"/>
-      <c r="J30" s="36" t="n"/>
+      <c r="I30" s="91" t="n"/>
+      <c r="J30" s="53" t="n"/>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="28" t="n"/>
@@ -4260,9 +4774,10 @@
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="89" t="n"/>
-      <c r="H31" s="91" t="n"/>
-      <c r="I31" s="54" t="n"/>
-      <c r="J31" s="28" t="n"/>
+      <c r="H31" s="92" t="n"/>
+      <c r="I31" s="93" t="n"/>
+      <c r="J31" s="54" t="n"/>
+      <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -4273,8 +4788,9 @@
       <c r="F32" s="40" t="n"/>
       <c r="G32" s="89" t="n"/>
       <c r="H32" s="90" t="n"/>
-      <c r="I32" s="53" t="n"/>
-      <c r="J32" s="36" t="n"/>
+      <c r="I32" s="91" t="n"/>
+      <c r="J32" s="53" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
@@ -4284,9 +4800,10 @@
       <c r="E33" s="32" t="n"/>
       <c r="F33" s="32" t="n"/>
       <c r="G33" s="89" t="n"/>
-      <c r="H33" s="91" t="n"/>
-      <c r="I33" s="54" t="n"/>
-      <c r="J33" s="28" t="n"/>
+      <c r="H33" s="92" t="n"/>
+      <c r="I33" s="93" t="n"/>
+      <c r="J33" s="54" t="n"/>
+      <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -4297,8 +4814,9 @@
       <c r="F34" s="40" t="n"/>
       <c r="G34" s="89" t="n"/>
       <c r="H34" s="90" t="n"/>
-      <c r="I34" s="53" t="n"/>
-      <c r="J34" s="36" t="n"/>
+      <c r="I34" s="91" t="n"/>
+      <c r="J34" s="53" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="20.4" customHeight="1">
       <c r="A35" s="28" t="n"/>
@@ -4308,9 +4826,10 @@
       <c r="E35" s="32" t="n"/>
       <c r="F35" s="32" t="n"/>
       <c r="G35" s="89" t="n"/>
-      <c r="H35" s="91" t="n"/>
-      <c r="I35" s="54" t="n"/>
-      <c r="J35" s="28" t="n"/>
+      <c r="H35" s="92" t="n"/>
+      <c r="I35" s="93" t="n"/>
+      <c r="J35" s="54" t="n"/>
+      <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="30.6" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -4321,8 +4840,9 @@
       <c r="F36" s="40" t="n"/>
       <c r="G36" s="89" t="n"/>
       <c r="H36" s="90" t="n"/>
-      <c r="I36" s="53" t="n"/>
-      <c r="J36" s="36" t="n"/>
+      <c r="I36" s="91" t="n"/>
+      <c r="J36" s="53" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="30.6" customHeight="1">
       <c r="A37" s="28" t="n"/>
@@ -4332,9 +4852,10 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="89" t="n"/>
-      <c r="H37" s="91" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="28" t="n"/>
+      <c r="H37" s="92" t="n"/>
+      <c r="I37" s="93" t="n"/>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -4345,8 +4866,9 @@
       <c r="F38" s="40" t="n"/>
       <c r="G38" s="89" t="n"/>
       <c r="H38" s="90" t="n"/>
-      <c r="I38" s="53" t="n"/>
-      <c r="J38" s="36" t="n"/>
+      <c r="I38" s="91" t="n"/>
+      <c r="J38" s="53" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
@@ -4356,9 +4878,10 @@
       <c r="E39" s="32" t="n"/>
       <c r="F39" s="32" t="n"/>
       <c r="G39" s="89" t="n"/>
-      <c r="H39" s="91" t="n"/>
-      <c r="I39" s="54" t="n"/>
-      <c r="J39" s="28" t="n"/>
+      <c r="H39" s="92" t="n"/>
+      <c r="I39" s="93" t="n"/>
+      <c r="J39" s="54" t="n"/>
+      <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="36" t="n"/>
@@ -4369,8 +4892,9 @@
       <c r="F40" s="40" t="n"/>
       <c r="G40" s="89" t="n"/>
       <c r="H40" s="90" t="n"/>
-      <c r="I40" s="53" t="n"/>
-      <c r="J40" s="36" t="n"/>
+      <c r="I40" s="91" t="n"/>
+      <c r="J40" s="53" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="30.6" customHeight="1">
       <c r="A41" s="28" t="n"/>
@@ -4380,222 +4904,121 @@
       <c r="E41" s="32" t="n"/>
       <c r="F41" s="32" t="n"/>
       <c r="G41" s="89" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="28" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" thickBot="1">
+      <c r="H41" s="92" t="n"/>
+      <c r="I41" s="93" t="n"/>
+      <c r="J41" s="54" t="n"/>
+      <c r="K41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="24.6" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="48" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="90" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="75" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
+      <c r="B42" s="76" t="n"/>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="79" t="n"/>
+      <c r="F42" s="79" t="n"/>
+      <c r="G42" s="94" t="n"/>
+      <c r="H42" s="104" t="n"/>
+      <c r="I42" s="105" t="n"/>
+      <c r="J42" s="81" t="n"/>
+      <c r="K42" s="75" t="n"/>
+    </row>
+    <row r="43">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="91" t="n"/>
-      <c r="I43" s="54" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="97" t="n"/>
+      <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" thickBot="1">
+      <c r="K43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="15.6" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="48" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="90" t="n"/>
-      <c r="I44" s="53" t="n"/>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="43" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="97" t="n"/>
+      <c r="I44" s="43" t="n"/>
       <c r="J44" s="43" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+      <c r="K44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="10.2" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="91" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="43" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="B45" s="58" t="n"/>
+      <c r="C45" s="59" t="n"/>
+      <c r="D45" s="59" t="n"/>
+      <c r="E45" s="59" t="n"/>
+      <c r="F45" s="59" t="n"/>
+      <c r="G45" s="59" t="n"/>
+      <c r="H45" s="98" t="n"/>
+      <c r="I45" s="59" t="n"/>
+      <c r="J45" s="60" t="n"/>
+      <c r="K45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="15.6" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" thickBot="1">
+      <c r="B46" s="67" t="n"/>
+      <c r="C46" s="64" t="n"/>
+      <c r="D46" s="64" t="n"/>
+      <c r="E46" s="64" t="n"/>
+      <c r="F46" s="64" t="n"/>
+      <c r="G46" s="64" t="n"/>
+      <c r="H46" s="99" t="n"/>
+      <c r="I46" s="64" t="n"/>
+      <c r="J46" s="65" t="n"/>
+      <c r="K46" s="43" t="n"/>
+    </row>
+    <row r="47" ht="10.8" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="49" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="91" t="n"/>
-      <c r="I47" s="54" t="n"/>
-      <c r="J47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1">
+      <c r="B47" s="61" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="100" t="n"/>
+      <c r="I47" s="62" t="n"/>
+      <c r="J47" s="63" t="n"/>
+      <c r="K47" s="43" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="40" t="n"/>
-      <c r="F48" s="40" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="90" t="n"/>
-      <c r="I48" s="53" t="n"/>
+      <c r="B48" s="43" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="43" t="n"/>
+      <c r="E48" s="43" t="n"/>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="43" t="n"/>
+      <c r="H48" s="97" t="n"/>
+      <c r="I48" s="43" t="n"/>
       <c r="J48" s="43" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
+      <c r="K48" s="43" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="49" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="91" t="n"/>
-      <c r="I49" s="54" t="n"/>
-      <c r="J49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="90" t="n"/>
-      <c r="I50" s="53" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="91" t="n"/>
-      <c r="I51" s="54" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="B52" s="48" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="40" t="n"/>
-      <c r="F52" s="40" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="90" t="n"/>
-      <c r="I52" s="53" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="49" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="89" t="n"/>
-      <c r="H53" s="91" t="n"/>
-      <c r="I53" s="54" t="n"/>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="89" t="n"/>
-      <c r="H54" s="90" t="n"/>
-      <c r="I54" s="53" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="89" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="54" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
-      <c r="G56" s="89" t="n"/>
-      <c r="H56" s="90" t="n"/>
-      <c r="I56" s="53" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="B57" s="49" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="89" t="n"/>
-      <c r="H57" s="91" t="n"/>
-      <c r="I57" s="54" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="B58" s="48" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
-      <c r="G58" s="89" t="n"/>
-      <c r="H58" s="90" t="n"/>
-      <c r="I58" s="53" t="n"/>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="B59" s="49" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
-      <c r="G59" s="89" t="n"/>
-      <c r="H59" s="91" t="n"/>
-      <c r="I59" s="54" t="n"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="40" t="n"/>
-      <c r="F60" s="40" t="n"/>
-      <c r="G60" s="89" t="n"/>
-      <c r="H60" s="90" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="B49" s="47" t="n"/>
+      <c r="C49" s="47" t="n"/>
+      <c r="D49" s="47" t="n"/>
+      <c r="E49" s="47" t="n"/>
+      <c r="F49" s="47" t="n"/>
+      <c r="G49" s="47" t="n"/>
+      <c r="H49" s="101" t="n"/>
+      <c r="I49" s="47" t="n"/>
+      <c r="J49" s="47" t="n"/>
+      <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G60">
+  <conditionalFormatting sqref="G8:G42">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
@@ -4723,14 +5146,14 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="94" t="n"/>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
-      <c r="G11" s="94" t="n"/>
-      <c r="H11" s="94" t="n"/>
-      <c r="I11" s="94" t="n"/>
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="102" t="n"/>
+      <c r="D11" s="102" t="n"/>
+      <c r="E11" s="102" t="n"/>
+      <c r="F11" s="102" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
@@ -4806,7 +5229,7 @@
     <row r="13" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="95" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="38" t="n"/>
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="40" t="n"/>
@@ -5460,7 +5883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I415"/>
+  <dimension ref="A1:I500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5510,12 +5933,509 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
     <row r="112" ht="409.6" customHeight="1">
       <c r="I112" s="56" t="n"/>
     </row>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
     <row r="415" ht="409.6" customHeight="1">
       <c r="I415" s="56" t="n"/>
     </row>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -2184,8 +2184,8 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84" t="n"/>
-      <c r="J2" s="83" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="84" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="45" t="n"/>
@@ -2236,21 +2236,17 @@
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="24" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B7" s="27" t="inlineStr"/>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -2842,7 +2838,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G41">
     <cfRule type="colorScale" priority="1371">
@@ -3709,7 +3705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I535"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -3759,540 +3755,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4358,8 +3820,8 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84" t="n"/>
-      <c r="J2" s="83" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="84" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="44" t="n"/>
@@ -4410,21 +3872,17 @@
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="24" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B7" s="27" t="inlineStr"/>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -5016,7 +4474,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G42">
     <cfRule type="colorScale" priority="1351">
@@ -5883,7 +5341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I500"/>
+  <dimension ref="A1:I415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5933,509 +5391,12 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
     <row r="112" ht="409.6" customHeight="1">
       <c r="I112" s="56" t="n"/>
     </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
     <row r="415" ht="409.6" customHeight="1">
       <c r="I415" s="56" t="n"/>
     </row>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -2149,7 +2149,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.44140625" customWidth="1" style="11" min="2" max="2"/>
+    <col width="8.5" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="14" min="3" max="3"/>
     <col width="26" customWidth="1" style="15" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
@@ -3785,7 +3785,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.44140625" customWidth="1" style="11" min="2" max="2"/>
+    <col width="8.5" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="14" min="3" max="3"/>
     <col width="26" customWidth="1" style="15" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>

--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -213,6 +213,16 @@
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF6B7A8D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="16">
@@ -457,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -725,6 +735,24 @@
     </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2155,9 +2183,9 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="10" customWidth="1" style="14" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="14" customWidth="1" style="14" min="8" max="8"/>
+    <col width="56" customWidth="1" style="11" min="9" max="9"/>
+    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
     <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
@@ -2184,8 +2212,7 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="82" t="n"/>
-      <c r="I2" s="84" t="n"/>
+      <c r="H2" s="84" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="45" t="n"/>
@@ -2229,24 +2256,32 @@
     </row>
     <row r="6" ht="27.6" customHeight="1">
       <c r="A6" s="24" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Legend:  NEW = new this week    RPT = repeat (2–3 wks)    STRK = streak (4+ wks)</t>
+        </is>
+      </c>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="55" t="inlineStr">
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
+      <c r="J6" s="55" t="inlineStr">
+        <is>
+          <t>Chris White, CFA
+Head of Research</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -2274,19 +2309,15 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
+      <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -2294,11 +2325,11 @@
       <c r="B8" s="48" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
-      <c r="E8" s="40" t="n"/>
-      <c r="F8" s="40" t="n"/>
+      <c r="E8" s="106" t="n"/>
+      <c r="F8" s="106" t="n"/>
       <c r="G8" s="89" t="n"/>
-      <c r="H8" s="90" t="n"/>
-      <c r="I8" s="91" t="n"/>
+      <c r="H8" s="107" t="n"/>
+      <c r="I8" s="108" t="n"/>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
@@ -2307,11 +2338,11 @@
       <c r="B9" s="49" t="n"/>
       <c r="C9" s="30" t="n"/>
       <c r="D9" s="31" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="32" t="n"/>
+      <c r="E9" s="109" t="n"/>
+      <c r="F9" s="109" t="n"/>
       <c r="G9" s="89" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="93" t="n"/>
+      <c r="H9" s="110" t="n"/>
+      <c r="I9" s="111" t="n"/>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
@@ -2323,8 +2354,8 @@
       <c r="E10" s="40" t="n"/>
       <c r="F10" s="40" t="n"/>
       <c r="G10" s="89" t="n"/>
-      <c r="H10" s="90" t="n"/>
-      <c r="I10" s="91" t="n"/>
+      <c r="H10" s="91" t="n"/>
+      <c r="I10" s="53" t="n"/>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
@@ -2336,8 +2367,8 @@
       <c r="E11" s="32" t="n"/>
       <c r="F11" s="32" t="n"/>
       <c r="G11" s="89" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="54" t="n"/>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
@@ -2349,8 +2380,8 @@
       <c r="E12" s="40" t="n"/>
       <c r="F12" s="40" t="n"/>
       <c r="G12" s="89" t="n"/>
-      <c r="H12" s="90" t="n"/>
-      <c r="I12" s="91" t="n"/>
+      <c r="H12" s="91" t="n"/>
+      <c r="I12" s="53" t="n"/>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
@@ -2362,8 +2393,8 @@
       <c r="E13" s="32" t="n"/>
       <c r="F13" s="32" t="n"/>
       <c r="G13" s="89" t="n"/>
-      <c r="H13" s="92" t="n"/>
-      <c r="I13" s="93" t="n"/>
+      <c r="H13" s="93" t="n"/>
+      <c r="I13" s="54" t="n"/>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
@@ -2375,8 +2406,8 @@
       <c r="E14" s="40" t="n"/>
       <c r="F14" s="40" t="n"/>
       <c r="G14" s="89" t="n"/>
-      <c r="H14" s="90" t="n"/>
-      <c r="I14" s="91" t="n"/>
+      <c r="H14" s="91" t="n"/>
+      <c r="I14" s="53" t="n"/>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
@@ -2388,8 +2419,8 @@
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="32" t="n"/>
       <c r="G15" s="89" t="n"/>
-      <c r="H15" s="92" t="n"/>
-      <c r="I15" s="93" t="n"/>
+      <c r="H15" s="93" t="n"/>
+      <c r="I15" s="54" t="n"/>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
@@ -2401,8 +2432,8 @@
       <c r="E16" s="32" t="n"/>
       <c r="F16" s="32" t="n"/>
       <c r="G16" s="89" t="n"/>
-      <c r="H16" s="92" t="n"/>
-      <c r="I16" s="93" t="n"/>
+      <c r="H16" s="93" t="n"/>
+      <c r="I16" s="54" t="n"/>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
@@ -2414,8 +2445,8 @@
       <c r="E17" s="40" t="n"/>
       <c r="F17" s="40" t="n"/>
       <c r="G17" s="89" t="n"/>
-      <c r="H17" s="90" t="n"/>
-      <c r="I17" s="91" t="n"/>
+      <c r="H17" s="91" t="n"/>
+      <c r="I17" s="53" t="n"/>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
@@ -2427,8 +2458,8 @@
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="32" t="n"/>
       <c r="G18" s="89" t="n"/>
-      <c r="H18" s="92" t="n"/>
-      <c r="I18" s="93" t="n"/>
+      <c r="H18" s="93" t="n"/>
+      <c r="I18" s="54" t="n"/>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
@@ -2440,8 +2471,8 @@
       <c r="E19" s="40" t="n"/>
       <c r="F19" s="40" t="n"/>
       <c r="G19" s="89" t="n"/>
-      <c r="H19" s="90" t="n"/>
-      <c r="I19" s="91" t="n"/>
+      <c r="H19" s="91" t="n"/>
+      <c r="I19" s="53" t="n"/>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
@@ -2453,8 +2484,8 @@
       <c r="E20" s="32" t="n"/>
       <c r="F20" s="32" t="n"/>
       <c r="G20" s="89" t="n"/>
-      <c r="H20" s="92" t="n"/>
-      <c r="I20" s="93" t="n"/>
+      <c r="H20" s="93" t="n"/>
+      <c r="I20" s="54" t="n"/>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
@@ -2466,8 +2497,8 @@
       <c r="E21" s="40" t="n"/>
       <c r="F21" s="40" t="n"/>
       <c r="G21" s="89" t="n"/>
-      <c r="H21" s="90" t="n"/>
-      <c r="I21" s="91" t="n"/>
+      <c r="H21" s="91" t="n"/>
+      <c r="I21" s="53" t="n"/>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
@@ -2479,8 +2510,8 @@
       <c r="E22" s="32" t="n"/>
       <c r="F22" s="32" t="n"/>
       <c r="G22" s="89" t="n"/>
-      <c r="H22" s="92" t="n"/>
-      <c r="I22" s="93" t="n"/>
+      <c r="H22" s="93" t="n"/>
+      <c r="I22" s="54" t="n"/>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
@@ -2492,8 +2523,8 @@
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="89" t="n"/>
-      <c r="H23" s="92" t="n"/>
-      <c r="I23" s="93" t="n"/>
+      <c r="H23" s="93" t="n"/>
+      <c r="I23" s="54" t="n"/>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
@@ -2505,8 +2536,8 @@
       <c r="E24" s="40" t="n"/>
       <c r="F24" s="40" t="n"/>
       <c r="G24" s="89" t="n"/>
-      <c r="H24" s="90" t="n"/>
-      <c r="I24" s="91" t="n"/>
+      <c r="H24" s="91" t="n"/>
+      <c r="I24" s="53" t="n"/>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
@@ -2518,8 +2549,8 @@
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="89" t="n"/>
-      <c r="H25" s="92" t="n"/>
-      <c r="I25" s="93" t="n"/>
+      <c r="H25" s="93" t="n"/>
+      <c r="I25" s="54" t="n"/>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
@@ -2531,8 +2562,8 @@
       <c r="E26" s="40" t="n"/>
       <c r="F26" s="40" t="n"/>
       <c r="G26" s="89" t="n"/>
-      <c r="H26" s="90" t="n"/>
-      <c r="I26" s="91" t="n"/>
+      <c r="H26" s="91" t="n"/>
+      <c r="I26" s="53" t="n"/>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
@@ -2544,8 +2575,8 @@
       <c r="E27" s="40" t="n"/>
       <c r="F27" s="40" t="n"/>
       <c r="G27" s="89" t="n"/>
-      <c r="H27" s="90" t="n"/>
-      <c r="I27" s="91" t="n"/>
+      <c r="H27" s="91" t="n"/>
+      <c r="I27" s="53" t="n"/>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
@@ -2557,8 +2588,8 @@
       <c r="E28" s="32" t="n"/>
       <c r="F28" s="32" t="n"/>
       <c r="G28" s="89" t="n"/>
-      <c r="H28" s="92" t="n"/>
-      <c r="I28" s="93" t="n"/>
+      <c r="H28" s="93" t="n"/>
+      <c r="I28" s="54" t="n"/>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
@@ -2570,8 +2601,8 @@
       <c r="E29" s="40" t="n"/>
       <c r="F29" s="40" t="n"/>
       <c r="G29" s="89" t="n"/>
-      <c r="H29" s="90" t="n"/>
-      <c r="I29" s="91" t="n"/>
+      <c r="H29" s="91" t="n"/>
+      <c r="I29" s="53" t="n"/>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
@@ -2583,8 +2614,8 @@
       <c r="E30" s="40" t="n"/>
       <c r="F30" s="40" t="n"/>
       <c r="G30" s="89" t="n"/>
-      <c r="H30" s="90" t="n"/>
-      <c r="I30" s="91" t="n"/>
+      <c r="H30" s="91" t="n"/>
+      <c r="I30" s="53" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
@@ -2596,8 +2627,8 @@
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="89" t="n"/>
-      <c r="H31" s="92" t="n"/>
-      <c r="I31" s="93" t="n"/>
+      <c r="H31" s="93" t="n"/>
+      <c r="I31" s="54" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
@@ -2609,8 +2640,8 @@
       <c r="E32" s="40" t="n"/>
       <c r="F32" s="40" t="n"/>
       <c r="G32" s="89" t="n"/>
-      <c r="H32" s="90" t="n"/>
-      <c r="I32" s="91" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
@@ -2622,8 +2653,8 @@
       <c r="E33" s="32" t="n"/>
       <c r="F33" s="32" t="n"/>
       <c r="G33" s="89" t="n"/>
-      <c r="H33" s="92" t="n"/>
-      <c r="I33" s="93" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="54" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
@@ -2635,8 +2666,8 @@
       <c r="E34" s="40" t="n"/>
       <c r="F34" s="40" t="n"/>
       <c r="G34" s="89" t="n"/>
-      <c r="H34" s="90" t="n"/>
-      <c r="I34" s="91" t="n"/>
+      <c r="H34" s="91" t="n"/>
+      <c r="I34" s="53" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
@@ -2648,8 +2679,8 @@
       <c r="E35" s="32" t="n"/>
       <c r="F35" s="32" t="n"/>
       <c r="G35" s="89" t="n"/>
-      <c r="H35" s="92" t="n"/>
-      <c r="I35" s="93" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="54" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
@@ -2661,8 +2692,8 @@
       <c r="E36" s="40" t="n"/>
       <c r="F36" s="40" t="n"/>
       <c r="G36" s="89" t="n"/>
-      <c r="H36" s="90" t="n"/>
-      <c r="I36" s="91" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
@@ -2674,8 +2705,8 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="89" t="n"/>
-      <c r="H37" s="92" t="n"/>
-      <c r="I37" s="93" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="54" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -2687,8 +2718,8 @@
       <c r="E38" s="40" t="n"/>
       <c r="F38" s="40" t="n"/>
       <c r="G38" s="89" t="n"/>
-      <c r="H38" s="90" t="n"/>
-      <c r="I38" s="91" t="n"/>
+      <c r="H38" s="91" t="n"/>
+      <c r="I38" s="53" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
@@ -2700,8 +2731,8 @@
       <c r="E39" s="32" t="n"/>
       <c r="F39" s="32" t="n"/>
       <c r="G39" s="89" t="n"/>
-      <c r="H39" s="92" t="n"/>
-      <c r="I39" s="93" t="n"/>
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="54" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
@@ -2713,8 +2744,8 @@
       <c r="E40" s="40" t="n"/>
       <c r="F40" s="40" t="n"/>
       <c r="G40" s="89" t="n"/>
-      <c r="H40" s="90" t="n"/>
-      <c r="I40" s="91" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="53" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
@@ -2726,8 +2757,8 @@
       <c r="E41" s="72" t="n"/>
       <c r="F41" s="72" t="n"/>
       <c r="G41" s="94" t="n"/>
-      <c r="H41" s="95" t="n"/>
-      <c r="I41" s="96" t="n"/>
+      <c r="H41" s="96" t="n"/>
+      <c r="I41" s="74" t="n"/>
       <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
@@ -2739,7 +2770,7 @@
       <c r="E42" s="43" t="n"/>
       <c r="F42" s="43" t="n"/>
       <c r="G42" s="43" t="n"/>
-      <c r="H42" s="97" t="n"/>
+      <c r="H42" s="43" t="n"/>
       <c r="I42" s="43" t="n"/>
       <c r="J42" s="43" t="n"/>
       <c r="K42" s="43" t="n"/>
@@ -2752,7 +2783,7 @@
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="43" t="n"/>
       <c r="G43" s="43" t="n"/>
-      <c r="H43" s="97" t="n"/>
+      <c r="H43" s="43" t="n"/>
       <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
@@ -2765,8 +2796,8 @@
       <c r="E44" s="59" t="n"/>
       <c r="F44" s="59" t="n"/>
       <c r="G44" s="59" t="n"/>
-      <c r="H44" s="98" t="n"/>
-      <c r="I44" s="59" t="n"/>
+      <c r="H44" s="59" t="n"/>
+      <c r="I44" s="60" t="n"/>
       <c r="J44" s="60" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
@@ -2778,8 +2809,8 @@
       <c r="E45" s="64" t="n"/>
       <c r="F45" s="64" t="n"/>
       <c r="G45" s="64" t="n"/>
-      <c r="H45" s="99" t="n"/>
-      <c r="I45" s="64" t="n"/>
+      <c r="H45" s="64" t="n"/>
+      <c r="I45" s="65" t="n"/>
       <c r="J45" s="65" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
@@ -2791,8 +2822,8 @@
       <c r="E46" s="62" t="n"/>
       <c r="F46" s="62" t="n"/>
       <c r="G46" s="62" t="n"/>
-      <c r="H46" s="100" t="n"/>
-      <c r="I46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="63" t="n"/>
       <c r="J46" s="63" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
@@ -2804,7 +2835,7 @@
       <c r="E47" s="43" t="n"/>
       <c r="F47" s="43" t="n"/>
       <c r="G47" s="43" t="n"/>
-      <c r="H47" s="97" t="n"/>
+      <c r="H47" s="43" t="n"/>
       <c r="I47" s="43" t="n"/>
       <c r="J47" s="43" t="n"/>
       <c r="K47" s="43" t="n"/>
@@ -2817,7 +2848,7 @@
       <c r="E48" s="47" t="n"/>
       <c r="F48" s="47" t="n"/>
       <c r="G48" s="47" t="n"/>
-      <c r="H48" s="101" t="n"/>
+      <c r="H48" s="47" t="n"/>
       <c r="I48" s="47" t="n"/>
       <c r="J48" s="47" t="n"/>
       <c r="K48" s="43" t="n"/>
@@ -2830,15 +2861,16 @@
       <c r="E49" s="43" t="n"/>
       <c r="F49" s="43" t="n"/>
       <c r="G49" s="43" t="n"/>
-      <c r="H49" s="97" t="n"/>
+      <c r="H49" s="43" t="n"/>
       <c r="I49" s="43" t="n"/>
       <c r="J49" s="43" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G41">
     <cfRule type="colorScale" priority="1371">
@@ -3791,9 +3823,9 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="10" customWidth="1" style="14" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="14" customWidth="1" style="14" min="8" max="8"/>
+    <col width="56" customWidth="1" style="11" min="9" max="9"/>
+    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
     <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
@@ -3820,8 +3852,7 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="82" t="n"/>
-      <c r="I2" s="84" t="n"/>
+      <c r="H2" s="84" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="44" t="n"/>
@@ -3865,24 +3896,32 @@
     </row>
     <row r="6" ht="27.6" customHeight="1">
       <c r="A6" s="24" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Legend:  NEW = new this week    RPT = repeat (2–3 wks)    STRK = streak (4+ wks)</t>
+        </is>
+      </c>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="55" t="inlineStr">
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
+      <c r="J6" s="55" t="inlineStr">
+        <is>
+          <t>Chris White, CFA
+Head of Research</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -3910,19 +3949,15 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
+      <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -3930,11 +3965,11 @@
       <c r="B8" s="48" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
-      <c r="E8" s="40" t="n"/>
-      <c r="F8" s="40" t="n"/>
+      <c r="E8" s="106" t="n"/>
+      <c r="F8" s="106" t="n"/>
       <c r="G8" s="89" t="n"/>
-      <c r="H8" s="90" t="n"/>
-      <c r="I8" s="91" t="n"/>
+      <c r="H8" s="107" t="n"/>
+      <c r="I8" s="108" t="n"/>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
@@ -3943,11 +3978,11 @@
       <c r="B9" s="49" t="n"/>
       <c r="C9" s="30" t="n"/>
       <c r="D9" s="31" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="32" t="n"/>
+      <c r="E9" s="109" t="n"/>
+      <c r="F9" s="109" t="n"/>
       <c r="G9" s="89" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="93" t="n"/>
+      <c r="H9" s="110" t="n"/>
+      <c r="I9" s="111" t="n"/>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
@@ -3959,8 +3994,8 @@
       <c r="E10" s="40" t="n"/>
       <c r="F10" s="40" t="n"/>
       <c r="G10" s="89" t="n"/>
-      <c r="H10" s="90" t="n"/>
-      <c r="I10" s="91" t="n"/>
+      <c r="H10" s="91" t="n"/>
+      <c r="I10" s="53" t="n"/>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
@@ -3972,8 +4007,8 @@
       <c r="E11" s="32" t="n"/>
       <c r="F11" s="32" t="n"/>
       <c r="G11" s="89" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="54" t="n"/>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
@@ -3985,8 +4020,8 @@
       <c r="E12" s="40" t="n"/>
       <c r="F12" s="40" t="n"/>
       <c r="G12" s="89" t="n"/>
-      <c r="H12" s="90" t="n"/>
-      <c r="I12" s="91" t="n"/>
+      <c r="H12" s="91" t="n"/>
+      <c r="I12" s="53" t="n"/>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
@@ -3998,8 +4033,8 @@
       <c r="E13" s="32" t="n"/>
       <c r="F13" s="32" t="n"/>
       <c r="G13" s="89" t="n"/>
-      <c r="H13" s="92" t="n"/>
-      <c r="I13" s="93" t="n"/>
+      <c r="H13" s="93" t="n"/>
+      <c r="I13" s="54" t="n"/>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
@@ -4011,8 +4046,8 @@
       <c r="E14" s="40" t="n"/>
       <c r="F14" s="40" t="n"/>
       <c r="G14" s="89" t="n"/>
-      <c r="H14" s="90" t="n"/>
-      <c r="I14" s="91" t="n"/>
+      <c r="H14" s="91" t="n"/>
+      <c r="I14" s="53" t="n"/>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
@@ -4024,8 +4059,8 @@
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="32" t="n"/>
       <c r="G15" s="89" t="n"/>
-      <c r="H15" s="92" t="n"/>
-      <c r="I15" s="93" t="n"/>
+      <c r="H15" s="93" t="n"/>
+      <c r="I15" s="54" t="n"/>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
@@ -4037,8 +4072,8 @@
       <c r="E16" s="40" t="n"/>
       <c r="F16" s="40" t="n"/>
       <c r="G16" s="89" t="n"/>
-      <c r="H16" s="90" t="n"/>
-      <c r="I16" s="91" t="n"/>
+      <c r="H16" s="91" t="n"/>
+      <c r="I16" s="53" t="n"/>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
@@ -4050,8 +4085,8 @@
       <c r="E17" s="32" t="n"/>
       <c r="F17" s="32" t="n"/>
       <c r="G17" s="89" t="n"/>
-      <c r="H17" s="92" t="n"/>
-      <c r="I17" s="93" t="n"/>
+      <c r="H17" s="93" t="n"/>
+      <c r="I17" s="54" t="n"/>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
@@ -4063,8 +4098,8 @@
       <c r="E18" s="40" t="n"/>
       <c r="F18" s="40" t="n"/>
       <c r="G18" s="89" t="n"/>
-      <c r="H18" s="90" t="n"/>
-      <c r="I18" s="91" t="n"/>
+      <c r="H18" s="91" t="n"/>
+      <c r="I18" s="53" t="n"/>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
@@ -4076,8 +4111,8 @@
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="32" t="n"/>
       <c r="G19" s="89" t="n"/>
-      <c r="H19" s="92" t="n"/>
-      <c r="I19" s="93" t="n"/>
+      <c r="H19" s="93" t="n"/>
+      <c r="I19" s="54" t="n"/>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
@@ -4089,8 +4124,8 @@
       <c r="E20" s="40" t="n"/>
       <c r="F20" s="40" t="n"/>
       <c r="G20" s="89" t="n"/>
-      <c r="H20" s="90" t="n"/>
-      <c r="I20" s="91" t="n"/>
+      <c r="H20" s="91" t="n"/>
+      <c r="I20" s="53" t="n"/>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
@@ -4102,8 +4137,8 @@
       <c r="E21" s="32" t="n"/>
       <c r="F21" s="32" t="n"/>
       <c r="G21" s="89" t="n"/>
-      <c r="H21" s="92" t="n"/>
-      <c r="I21" s="93" t="n"/>
+      <c r="H21" s="93" t="n"/>
+      <c r="I21" s="54" t="n"/>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
@@ -4115,8 +4150,8 @@
       <c r="E22" s="40" t="n"/>
       <c r="F22" s="40" t="n"/>
       <c r="G22" s="89" t="n"/>
-      <c r="H22" s="90" t="n"/>
-      <c r="I22" s="91" t="n"/>
+      <c r="H22" s="91" t="n"/>
+      <c r="I22" s="53" t="n"/>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
@@ -4128,8 +4163,8 @@
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="89" t="n"/>
-      <c r="H23" s="92" t="n"/>
-      <c r="I23" s="93" t="n"/>
+      <c r="H23" s="93" t="n"/>
+      <c r="I23" s="54" t="n"/>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
@@ -4141,8 +4176,8 @@
       <c r="E24" s="40" t="n"/>
       <c r="F24" s="40" t="n"/>
       <c r="G24" s="89" t="n"/>
-      <c r="H24" s="90" t="n"/>
-      <c r="I24" s="91" t="n"/>
+      <c r="H24" s="91" t="n"/>
+      <c r="I24" s="53" t="n"/>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
@@ -4154,8 +4189,8 @@
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="89" t="n"/>
-      <c r="H25" s="92" t="n"/>
-      <c r="I25" s="93" t="n"/>
+      <c r="H25" s="93" t="n"/>
+      <c r="I25" s="54" t="n"/>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
@@ -4167,8 +4202,8 @@
       <c r="E26" s="40" t="n"/>
       <c r="F26" s="40" t="n"/>
       <c r="G26" s="89" t="n"/>
-      <c r="H26" s="90" t="n"/>
-      <c r="I26" s="91" t="n"/>
+      <c r="H26" s="91" t="n"/>
+      <c r="I26" s="53" t="n"/>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
@@ -4180,8 +4215,8 @@
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="89" t="n"/>
-      <c r="H27" s="92" t="n"/>
-      <c r="I27" s="93" t="n"/>
+      <c r="H27" s="93" t="n"/>
+      <c r="I27" s="54" t="n"/>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
@@ -4193,8 +4228,8 @@
       <c r="E28" s="40" t="n"/>
       <c r="F28" s="40" t="n"/>
       <c r="G28" s="89" t="n"/>
-      <c r="H28" s="90" t="n"/>
-      <c r="I28" s="91" t="n"/>
+      <c r="H28" s="91" t="n"/>
+      <c r="I28" s="53" t="n"/>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
@@ -4206,8 +4241,8 @@
       <c r="E29" s="32" t="n"/>
       <c r="F29" s="32" t="n"/>
       <c r="G29" s="89" t="n"/>
-      <c r="H29" s="92" t="n"/>
-      <c r="I29" s="93" t="n"/>
+      <c r="H29" s="93" t="n"/>
+      <c r="I29" s="54" t="n"/>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
@@ -4219,8 +4254,8 @@
       <c r="E30" s="40" t="n"/>
       <c r="F30" s="40" t="n"/>
       <c r="G30" s="89" t="n"/>
-      <c r="H30" s="90" t="n"/>
-      <c r="I30" s="91" t="n"/>
+      <c r="H30" s="91" t="n"/>
+      <c r="I30" s="53" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
@@ -4232,8 +4267,8 @@
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="89" t="n"/>
-      <c r="H31" s="92" t="n"/>
-      <c r="I31" s="93" t="n"/>
+      <c r="H31" s="93" t="n"/>
+      <c r="I31" s="54" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
@@ -4245,8 +4280,8 @@
       <c r="E32" s="40" t="n"/>
       <c r="F32" s="40" t="n"/>
       <c r="G32" s="89" t="n"/>
-      <c r="H32" s="90" t="n"/>
-      <c r="I32" s="91" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
@@ -4258,8 +4293,8 @@
       <c r="E33" s="32" t="n"/>
       <c r="F33" s="32" t="n"/>
       <c r="G33" s="89" t="n"/>
-      <c r="H33" s="92" t="n"/>
-      <c r="I33" s="93" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="54" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
@@ -4271,8 +4306,8 @@
       <c r="E34" s="40" t="n"/>
       <c r="F34" s="40" t="n"/>
       <c r="G34" s="89" t="n"/>
-      <c r="H34" s="90" t="n"/>
-      <c r="I34" s="91" t="n"/>
+      <c r="H34" s="91" t="n"/>
+      <c r="I34" s="53" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
@@ -4284,8 +4319,8 @@
       <c r="E35" s="32" t="n"/>
       <c r="F35" s="32" t="n"/>
       <c r="G35" s="89" t="n"/>
-      <c r="H35" s="92" t="n"/>
-      <c r="I35" s="93" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="54" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
@@ -4297,8 +4332,8 @@
       <c r="E36" s="40" t="n"/>
       <c r="F36" s="40" t="n"/>
       <c r="G36" s="89" t="n"/>
-      <c r="H36" s="90" t="n"/>
-      <c r="I36" s="91" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
@@ -4310,8 +4345,8 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="89" t="n"/>
-      <c r="H37" s="92" t="n"/>
-      <c r="I37" s="93" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="54" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -4323,8 +4358,8 @@
       <c r="E38" s="40" t="n"/>
       <c r="F38" s="40" t="n"/>
       <c r="G38" s="89" t="n"/>
-      <c r="H38" s="90" t="n"/>
-      <c r="I38" s="91" t="n"/>
+      <c r="H38" s="91" t="n"/>
+      <c r="I38" s="53" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
@@ -4336,8 +4371,8 @@
       <c r="E39" s="32" t="n"/>
       <c r="F39" s="32" t="n"/>
       <c r="G39" s="89" t="n"/>
-      <c r="H39" s="92" t="n"/>
-      <c r="I39" s="93" t="n"/>
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="54" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
@@ -4349,8 +4384,8 @@
       <c r="E40" s="40" t="n"/>
       <c r="F40" s="40" t="n"/>
       <c r="G40" s="89" t="n"/>
-      <c r="H40" s="90" t="n"/>
-      <c r="I40" s="91" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="53" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
@@ -4362,8 +4397,8 @@
       <c r="E41" s="32" t="n"/>
       <c r="F41" s="32" t="n"/>
       <c r="G41" s="89" t="n"/>
-      <c r="H41" s="92" t="n"/>
-      <c r="I41" s="93" t="n"/>
+      <c r="H41" s="93" t="n"/>
+      <c r="I41" s="54" t="n"/>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
@@ -4375,8 +4410,8 @@
       <c r="E42" s="79" t="n"/>
       <c r="F42" s="79" t="n"/>
       <c r="G42" s="94" t="n"/>
-      <c r="H42" s="104" t="n"/>
-      <c r="I42" s="105" t="n"/>
+      <c r="H42" s="105" t="n"/>
+      <c r="I42" s="81" t="n"/>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
@@ -4388,7 +4423,7 @@
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="43" t="n"/>
       <c r="G43" s="43" t="n"/>
-      <c r="H43" s="97" t="n"/>
+      <c r="H43" s="43" t="n"/>
       <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
@@ -4401,7 +4436,7 @@
       <c r="E44" s="43" t="n"/>
       <c r="F44" s="43" t="n"/>
       <c r="G44" s="43" t="n"/>
-      <c r="H44" s="97" t="n"/>
+      <c r="H44" s="43" t="n"/>
       <c r="I44" s="43" t="n"/>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
@@ -4414,8 +4449,8 @@
       <c r="E45" s="59" t="n"/>
       <c r="F45" s="59" t="n"/>
       <c r="G45" s="59" t="n"/>
-      <c r="H45" s="98" t="n"/>
-      <c r="I45" s="59" t="n"/>
+      <c r="H45" s="59" t="n"/>
+      <c r="I45" s="60" t="n"/>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
@@ -4427,8 +4462,8 @@
       <c r="E46" s="64" t="n"/>
       <c r="F46" s="64" t="n"/>
       <c r="G46" s="64" t="n"/>
-      <c r="H46" s="99" t="n"/>
-      <c r="I46" s="64" t="n"/>
+      <c r="H46" s="64" t="n"/>
+      <c r="I46" s="65" t="n"/>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
@@ -4440,8 +4475,8 @@
       <c r="E47" s="62" t="n"/>
       <c r="F47" s="62" t="n"/>
       <c r="G47" s="62" t="n"/>
-      <c r="H47" s="100" t="n"/>
-      <c r="I47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="63" t="n"/>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
@@ -4453,7 +4488,7 @@
       <c r="E48" s="43" t="n"/>
       <c r="F48" s="43" t="n"/>
       <c r="G48" s="43" t="n"/>
-      <c r="H48" s="97" t="n"/>
+      <c r="H48" s="43" t="n"/>
       <c r="I48" s="43" t="n"/>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
@@ -4466,15 +4501,16 @@
       <c r="E49" s="47" t="n"/>
       <c r="F49" s="47" t="n"/>
       <c r="G49" s="47" t="n"/>
-      <c r="H49" s="101" t="n"/>
+      <c r="H49" s="47" t="n"/>
       <c r="I49" s="47" t="n"/>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G42">
     <cfRule type="colorScale" priority="1351">

--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -753,6 +753,9 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2213,6 +2216,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n"/>
+      <c r="J2" s="83" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="45" t="n"/>
@@ -2268,12 +2272,7 @@
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="55" t="inlineStr">
-        <is>
-          <t>Chris White, CFA
-Head of Research</t>
-        </is>
-      </c>
+      <c r="J6" s="112" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
@@ -3853,6 +3852,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n"/>
+      <c r="J2" s="83" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="44" t="n"/>
@@ -3908,12 +3908,7 @@
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="55" t="inlineStr">
-        <is>
-          <t>Chris White, CFA
-Head of Research</t>
-        </is>
-      </c>
+      <c r="J6" s="112" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>

--- a/templates/benchmark_beaters_template.xlsx
+++ b/templates/benchmark_beaters_template.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="34">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -223,6 +223,40 @@
       <name val="Calibri"/>
       <color rgb="FF4B5563"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2563A8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF6B7A8D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF166534"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF4B5563"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="16">
@@ -467,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -754,8 +788,45 @@
     <xf numFmtId="0" fontId="27" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -770,172 +841,34 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <oneCellAnchor>
     <from>
       <col>8</col>
       <colOff>2268855</colOff>
       <row>0</row>
       <rowOff>76143</rowOff>
     </from>
-    <to>
-      <col>9</col>
-      <colOff>59055</colOff>
-      <row>1</row>
-      <rowOff>282839</rowOff>
-    </to>
+    <ext cx="1666875" cy="352425"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Picture 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9584055" y="76143"/>
-          <a:ext cx="1624965" cy="279086"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </pic>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>6</col>
-      <colOff>676230</colOff>
-      <row>4</row>
-      <rowOff>53556</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>880082</colOff>
-      <row>5</row>
-      <rowOff>244251</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Picture 11"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6129293" y="958431"/>
-          <a:ext cx="203852" cy="260466"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>907842</colOff>
-      <row>4</row>
-      <rowOff>69534</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>16690</colOff>
-      <row>5</row>
-      <rowOff>190501</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Picture 13"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3824873" y="974409"/>
-          <a:ext cx="196603" cy="198358"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>1131570</colOff>
-      <row>4</row>
-      <rowOff>53030</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>1353820</colOff>
-      <row>5</row>
-      <rowOff>224912</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Picture 18"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5163820" y="961080"/>
-          <a:ext cx="212725" cy="248082"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1192,172 +1125,34 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <oneCellAnchor>
     <from>
       <col>8</col>
       <colOff>2268855</colOff>
       <row>0</row>
       <rowOff>76143</rowOff>
     </from>
-    <to>
-      <col>9</col>
-      <colOff>59055</colOff>
-      <row>1</row>
-      <rowOff>282839</rowOff>
-    </to>
+    <ext cx="1666875" cy="352425"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Picture 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9580245" y="76143"/>
-          <a:ext cx="1628775" cy="286706"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </pic>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>6</col>
-      <colOff>676230</colOff>
-      <row>4</row>
-      <rowOff>53556</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>880082</colOff>
-      <row>5</row>
-      <rowOff>244251</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Picture 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6132150" y="962241"/>
-          <a:ext cx="205757" cy="266895"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>907842</colOff>
-      <row>4</row>
-      <rowOff>69534</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>16690</colOff>
-      <row>5</row>
-      <rowOff>190501</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Picture 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3830112" y="972504"/>
-          <a:ext cx="209938" cy="199072"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>1131570</colOff>
-      <row>4</row>
-      <rowOff>53030</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>1353820</colOff>
-      <row>5</row>
-      <rowOff>224912</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Picture 11"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5149215" y="961715"/>
-          <a:ext cx="220345" cy="244272"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2276,42 +2071,42 @@
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="113" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="113" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="114" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="114" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="114" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>6-Mo Return</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="113" t="inlineStr">
         <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="114" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
@@ -2322,26 +2117,26 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="48" t="n"/>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="39" t="n"/>
-      <c r="E8" s="106" t="n"/>
-      <c r="F8" s="106" t="n"/>
-      <c r="G8" s="89" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="108" t="n"/>
+      <c r="C8" s="115" t="n"/>
+      <c r="D8" s="116" t="n"/>
+      <c r="E8" s="117" t="n"/>
+      <c r="F8" s="117" t="n"/>
+      <c r="G8" s="118" t="n"/>
+      <c r="H8" s="119" t="n"/>
+      <c r="I8" s="120" t="n"/>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="26.4" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="49" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="109" t="n"/>
-      <c r="F9" s="109" t="n"/>
-      <c r="G9" s="89" t="n"/>
-      <c r="H9" s="110" t="n"/>
-      <c r="I9" s="111" t="n"/>
+      <c r="C9" s="121" t="n"/>
+      <c r="D9" s="122" t="n"/>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="123" t="n"/>
+      <c r="G9" s="118" t="n"/>
+      <c r="H9" s="124" t="n"/>
+      <c r="I9" s="125" t="n"/>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
@@ -3912,42 +3707,42 @@
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="113" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="113" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="114" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="114" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="114" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>6-Mo Return</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="113" t="inlineStr">
         <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="114" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
@@ -3958,26 +3753,26 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="48" t="n"/>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="39" t="n"/>
-      <c r="E8" s="106" t="n"/>
-      <c r="F8" s="106" t="n"/>
-      <c r="G8" s="89" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="108" t="n"/>
+      <c r="C8" s="115" t="n"/>
+      <c r="D8" s="116" t="n"/>
+      <c r="E8" s="117" t="n"/>
+      <c r="F8" s="117" t="n"/>
+      <c r="G8" s="118" t="n"/>
+      <c r="H8" s="119" t="n"/>
+      <c r="I8" s="120" t="n"/>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="49" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="109" t="n"/>
-      <c r="F9" s="109" t="n"/>
-      <c r="G9" s="89" t="n"/>
-      <c r="H9" s="110" t="n"/>
-      <c r="I9" s="111" t="n"/>
+      <c r="C9" s="121" t="n"/>
+      <c r="D9" s="122" t="n"/>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="123" t="n"/>
+      <c r="G9" s="118" t="n"/>
+      <c r="H9" s="124" t="n"/>
+      <c r="I9" s="125" t="n"/>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
